--- a/GameDesign/Excel/DropMining.xlsx
+++ b/GameDesign/Excel/DropMining.xlsx
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -367,6 +367,12 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -740,7 +746,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="13" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="15" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1061,27 +1067,63 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="46" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="47" t="n"/>
+      <c r="B16" s="50" t="n">
+        <v>300109</v>
+      </c>
+      <c r="C16" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50" t="n">
+        <v>100019</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="46" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="47" t="n"/>
+      <c r="B17" s="50" t="n">
+        <v>300110</v>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="50" t="n">
+        <v>100020</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>은 상자 Lv1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="47" t="n"/>
+      <c r="B18" s="50" t="n">
+        <v>300111</v>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>100021</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -3362,6 +3404,30 @@
       <c r="D303" s="46" t="n"/>
       <c r="E303" s="46" t="n"/>
       <c r="F303" s="47" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="46" t="n"/>
+      <c r="B304" s="46" t="n"/>
+      <c r="C304" s="46" t="n"/>
+      <c r="D304" s="46" t="n"/>
+      <c r="E304" s="46" t="n"/>
+      <c r="F304" s="47" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="46" t="n"/>
+      <c r="B305" s="46" t="n"/>
+      <c r="C305" s="46" t="n"/>
+      <c r="D305" s="46" t="n"/>
+      <c r="E305" s="46" t="n"/>
+      <c r="F305" s="47" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="46" t="n"/>
+      <c r="B306" s="46" t="n"/>
+      <c r="C306" s="46" t="n"/>
+      <c r="D306" s="46" t="n"/>
+      <c r="E306" s="46" t="n"/>
+      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -3384,7 +3450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -3392,7 +3458,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="27" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="15" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3713,51 +3779,63 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>300207</v>
-      </c>
-      <c r="C16" s="44" t="n">
+      <c r="B16" s="50" t="n">
+        <v>300209</v>
+      </c>
+      <c r="C16" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="44" t="n">
-        <v>40001</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>돌덩어리 — Lv1 하위 혼입</t>
+      <c r="D16" s="50" t="n">
+        <v>100022</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>300208</v>
-      </c>
-      <c r="C17" s="44" t="n">
+      <c r="B17" s="50" t="n">
+        <v>300210</v>
+      </c>
+      <c r="C17" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="44" t="n">
-        <v>40002</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>300</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>구리 광석 — Lv1 하위 혼입</t>
+      <c r="D17" s="50" t="n">
+        <v>100023</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>은 상자 Lv2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="47" t="n"/>
+      <c r="B18" s="50" t="n">
+        <v>300211</v>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>100024</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -6054,6 +6132,14 @@
       <c r="D305" s="46" t="n"/>
       <c r="E305" s="46" t="n"/>
       <c r="F305" s="47" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="46" t="n"/>
+      <c r="B306" s="46" t="n"/>
+      <c r="C306" s="46" t="n"/>
+      <c r="D306" s="46" t="n"/>
+      <c r="E306" s="46" t="n"/>
+      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -6076,7 +6162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -6084,7 +6170,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="27" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="15" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6405,51 +6491,63 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>300307</v>
-      </c>
-      <c r="C16" s="44" t="n">
+      <c r="B16" s="50" t="n">
+        <v>300309</v>
+      </c>
+      <c r="C16" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="44" t="n">
-        <v>40001</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>700</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>돌덩어리 — Lv1 하위 혼입</t>
+      <c r="D16" s="50" t="n">
+        <v>100025</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>300308</v>
-      </c>
-      <c r="C17" s="44" t="n">
+      <c r="B17" s="50" t="n">
+        <v>300310</v>
+      </c>
+      <c r="C17" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="44" t="n">
-        <v>40002</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>200</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>구리 광석 — Lv1 하위 혼입</t>
+      <c r="D17" s="50" t="n">
+        <v>100026</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>은 상자 Lv3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="47" t="n"/>
+      <c r="B18" s="50" t="n">
+        <v>300311</v>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>100027</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -8746,6 +8844,14 @@
       <c r="D305" s="46" t="n"/>
       <c r="E305" s="46" t="n"/>
       <c r="F305" s="47" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="46" t="n"/>
+      <c r="B306" s="46" t="n"/>
+      <c r="C306" s="46" t="n"/>
+      <c r="D306" s="46" t="n"/>
+      <c r="E306" s="46" t="n"/>
+      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -8768,7 +8874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -8776,7 +8882,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="27" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="17" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9097,51 +9203,63 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>300407</v>
-      </c>
-      <c r="C16" s="44" t="n">
+      <c r="B16" s="50" t="n">
+        <v>300409</v>
+      </c>
+      <c r="C16" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="44" t="n">
-        <v>40001</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>400</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>돌덩어리 — Lv1 하위 혼입</t>
+      <c r="D16" s="50" t="n">
+        <v>100028</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>300408</v>
-      </c>
-      <c r="C17" s="44" t="n">
+      <c r="B17" s="50" t="n">
+        <v>300410</v>
+      </c>
+      <c r="C17" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="44" t="n">
-        <v>40002</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>100</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>구리 광석 — Lv1 하위 혼입</t>
+      <c r="D17" s="50" t="n">
+        <v>100029</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>은 상자 Lv4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="47" t="n"/>
+      <c r="B18" s="50" t="n">
+        <v>300411</v>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>100030</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv4</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -11438,6 +11556,14 @@
       <c r="D305" s="46" t="n"/>
       <c r="E305" s="46" t="n"/>
       <c r="F305" s="47" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="46" t="n"/>
+      <c r="B306" s="46" t="n"/>
+      <c r="C306" s="46" t="n"/>
+      <c r="D306" s="46" t="n"/>
+      <c r="E306" s="46" t="n"/>
+      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -11460,7 +11586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -11468,7 +11594,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="27" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="18" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11789,51 +11915,63 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="44" t="n">
-        <v>300507</v>
-      </c>
-      <c r="C16" s="44" t="n">
+      <c r="B16" s="50" t="n">
+        <v>300509</v>
+      </c>
+      <c r="C16" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="44" t="n">
-        <v>40001</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>200</v>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>돌덩어리 — Lv1 하위 혼입</t>
+      <c r="D16" s="50" t="n">
+        <v>100031</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>205</v>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="44" t="n">
-        <v>300508</v>
-      </c>
-      <c r="C17" s="44" t="n">
+      <c r="B17" s="50" t="n">
+        <v>300510</v>
+      </c>
+      <c r="C17" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="44" t="n">
-        <v>40002</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>50</v>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>구리 광석 — Lv1 하위 혼입</t>
+      <c r="D17" s="50" t="n">
+        <v>100032</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>은 상자 Lv5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="47" t="n"/>
+      <c r="B18" s="50" t="n">
+        <v>300511</v>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>100033</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv5</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -14130,6 +14268,14 @@
       <c r="D305" s="46" t="n"/>
       <c r="E305" s="46" t="n"/>
       <c r="F305" s="47" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="46" t="n"/>
+      <c r="B306" s="46" t="n"/>
+      <c r="C306" s="46" t="n"/>
+      <c r="D306" s="46" t="n"/>
+      <c r="E306" s="46" t="n"/>
+      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/DropMining.xlsx
+++ b/GameDesign/Excel/DropMining.xlsx
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -746,7 +746,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="15" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="13" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,63 +1067,27 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="50" t="n">
-        <v>300109</v>
-      </c>
-      <c r="C16" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>100019</v>
-      </c>
-      <c r="E16" s="50" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv1</t>
-        </is>
-      </c>
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="47" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="50" t="n">
-        <v>300110</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>100020</v>
-      </c>
-      <c r="E17" s="50" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="51" t="inlineStr">
-        <is>
-          <t>은 상자 Lv1</t>
-        </is>
-      </c>
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="47" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="50" t="n">
-        <v>300111</v>
-      </c>
-      <c r="C18" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="50" t="n">
-        <v>100021</v>
-      </c>
-      <c r="E18" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv1</t>
-        </is>
-      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
+      <c r="E18" s="46" t="n"/>
+      <c r="F18" s="47" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -3404,30 +3368,6 @@
       <c r="D303" s="46" t="n"/>
       <c r="E303" s="46" t="n"/>
       <c r="F303" s="47" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="46" t="n"/>
-      <c r="B304" s="46" t="n"/>
-      <c r="C304" s="46" t="n"/>
-      <c r="D304" s="46" t="n"/>
-      <c r="E304" s="46" t="n"/>
-      <c r="F304" s="47" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="46" t="n"/>
-      <c r="B305" s="46" t="n"/>
-      <c r="C305" s="46" t="n"/>
-      <c r="D305" s="46" t="n"/>
-      <c r="E305" s="46" t="n"/>
-      <c r="F305" s="47" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="46" t="n"/>
-      <c r="B306" s="46" t="n"/>
-      <c r="C306" s="46" t="n"/>
-      <c r="D306" s="46" t="n"/>
-      <c r="E306" s="46" t="n"/>
-      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -3450,7 +3390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -3458,7 +3398,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="15" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="13" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3779,63 +3719,27 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="50" t="n">
-        <v>300209</v>
-      </c>
-      <c r="C16" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>100022</v>
-      </c>
-      <c r="E16" s="50" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv2</t>
-        </is>
-      </c>
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="47" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="50" t="n">
-        <v>300210</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>100023</v>
-      </c>
-      <c r="E17" s="50" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="51" t="inlineStr">
-        <is>
-          <t>은 상자 Lv2</t>
-        </is>
-      </c>
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="47" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="50" t="n">
-        <v>300211</v>
-      </c>
-      <c r="C18" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="50" t="n">
-        <v>100024</v>
-      </c>
-      <c r="E18" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv2</t>
-        </is>
-      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
+      <c r="E18" s="46" t="n"/>
+      <c r="F18" s="47" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -6116,30 +6020,6 @@
       <c r="D303" s="46" t="n"/>
       <c r="E303" s="46" t="n"/>
       <c r="F303" s="47" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="46" t="n"/>
-      <c r="B304" s="46" t="n"/>
-      <c r="C304" s="46" t="n"/>
-      <c r="D304" s="46" t="n"/>
-      <c r="E304" s="46" t="n"/>
-      <c r="F304" s="47" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="46" t="n"/>
-      <c r="B305" s="46" t="n"/>
-      <c r="C305" s="46" t="n"/>
-      <c r="D305" s="46" t="n"/>
-      <c r="E305" s="46" t="n"/>
-      <c r="F305" s="47" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="46" t="n"/>
-      <c r="B306" s="46" t="n"/>
-      <c r="C306" s="46" t="n"/>
-      <c r="D306" s="46" t="n"/>
-      <c r="E306" s="46" t="n"/>
-      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -6162,7 +6042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -6170,7 +6050,7 @@
     <col width="26" customWidth="1" style="10" min="3" max="3"/>
     <col width="19" customWidth="1" style="10" min="4" max="4"/>
     <col width="12" customWidth="1" style="10" min="5" max="5"/>
-    <col width="15" customWidth="1" style="10" min="6" max="16384"/>
+    <col width="13" customWidth="1" style="10" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6491,63 +6371,27 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="50" t="n">
-        <v>300309</v>
-      </c>
-      <c r="C16" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>100025</v>
-      </c>
-      <c r="E16" s="50" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv3</t>
-        </is>
-      </c>
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="47" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="50" t="n">
-        <v>300310</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>100026</v>
-      </c>
-      <c r="E17" s="50" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="51" t="inlineStr">
-        <is>
-          <t>은 상자 Lv3</t>
-        </is>
-      </c>
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="47" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="50" t="n">
-        <v>300311</v>
-      </c>
-      <c r="C18" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="50" t="n">
-        <v>100027</v>
-      </c>
-      <c r="E18" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv3</t>
-        </is>
-      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
+      <c r="E18" s="46" t="n"/>
+      <c r="F18" s="47" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -8828,30 +8672,6 @@
       <c r="D303" s="46" t="n"/>
       <c r="E303" s="46" t="n"/>
       <c r="F303" s="47" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="46" t="n"/>
-      <c r="B304" s="46" t="n"/>
-      <c r="C304" s="46" t="n"/>
-      <c r="D304" s="46" t="n"/>
-      <c r="E304" s="46" t="n"/>
-      <c r="F304" s="47" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="46" t="n"/>
-      <c r="B305" s="46" t="n"/>
-      <c r="C305" s="46" t="n"/>
-      <c r="D305" s="46" t="n"/>
-      <c r="E305" s="46" t="n"/>
-      <c r="F305" s="47" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="46" t="n"/>
-      <c r="B306" s="46" t="n"/>
-      <c r="C306" s="46" t="n"/>
-      <c r="D306" s="46" t="n"/>
-      <c r="E306" s="46" t="n"/>
-      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -8874,7 +8694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -9203,63 +9023,27 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="50" t="n">
-        <v>300409</v>
-      </c>
-      <c r="C16" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>100028</v>
-      </c>
-      <c r="E16" s="50" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv4</t>
-        </is>
-      </c>
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="47" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="50" t="n">
-        <v>300410</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>100029</v>
-      </c>
-      <c r="E17" s="50" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="51" t="inlineStr">
-        <is>
-          <t>은 상자 Lv4</t>
-        </is>
-      </c>
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="47" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="50" t="n">
-        <v>300411</v>
-      </c>
-      <c r="C18" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="50" t="n">
-        <v>100030</v>
-      </c>
-      <c r="E18" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv4</t>
-        </is>
-      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
+      <c r="E18" s="46" t="n"/>
+      <c r="F18" s="47" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -11540,30 +11324,6 @@
       <c r="D303" s="46" t="n"/>
       <c r="E303" s="46" t="n"/>
       <c r="F303" s="47" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="46" t="n"/>
-      <c r="B304" s="46" t="n"/>
-      <c r="C304" s="46" t="n"/>
-      <c r="D304" s="46" t="n"/>
-      <c r="E304" s="46" t="n"/>
-      <c r="F304" s="47" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="46" t="n"/>
-      <c r="B305" s="46" t="n"/>
-      <c r="C305" s="46" t="n"/>
-      <c r="D305" s="46" t="n"/>
-      <c r="E305" s="46" t="n"/>
-      <c r="F305" s="47" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="46" t="n"/>
-      <c r="B306" s="46" t="n"/>
-      <c r="C306" s="46" t="n"/>
-      <c r="D306" s="46" t="n"/>
-      <c r="E306" s="46" t="n"/>
-      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -11586,7 +11346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.090624999999999" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" style="10" min="1" max="1"/>
@@ -11915,63 +11675,27 @@
     </row>
     <row r="16">
       <c r="A16" s="46" t="n"/>
-      <c r="B16" s="50" t="n">
-        <v>300509</v>
-      </c>
-      <c r="C16" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="50" t="n">
-        <v>100031</v>
-      </c>
-      <c r="E16" s="50" t="n">
-        <v>205</v>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
-        <is>
-          <t>나무 상자 Lv5</t>
-        </is>
-      </c>
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="47" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="46" t="n"/>
-      <c r="B17" s="50" t="n">
-        <v>300510</v>
-      </c>
-      <c r="C17" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="50" t="n">
-        <v>100032</v>
-      </c>
-      <c r="E17" s="50" t="n">
-        <v>31</v>
-      </c>
-      <c r="F17" s="51" t="inlineStr">
-        <is>
-          <t>은 상자 Lv5</t>
-        </is>
-      </c>
+      <c r="B17" s="46" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="47" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="46" t="n"/>
-      <c r="B18" s="50" t="n">
-        <v>300511</v>
-      </c>
-      <c r="C18" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="50" t="n">
-        <v>100033</v>
-      </c>
-      <c r="E18" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>황금 상자 Lv5</t>
-        </is>
-      </c>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
+      <c r="E18" s="46" t="n"/>
+      <c r="F18" s="47" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="46" t="n"/>
@@ -14252,30 +13976,6 @@
       <c r="D303" s="46" t="n"/>
       <c r="E303" s="46" t="n"/>
       <c r="F303" s="47" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="46" t="n"/>
-      <c r="B304" s="46" t="n"/>
-      <c r="C304" s="46" t="n"/>
-      <c r="D304" s="46" t="n"/>
-      <c r="E304" s="46" t="n"/>
-      <c r="F304" s="47" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="46" t="n"/>
-      <c r="B305" s="46" t="n"/>
-      <c r="C305" s="46" t="n"/>
-      <c r="D305" s="46" t="n"/>
-      <c r="E305" s="46" t="n"/>
-      <c r="F305" s="47" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="46" t="n"/>
-      <c r="B306" s="46" t="n"/>
-      <c r="C306" s="46" t="n"/>
-      <c r="D306" s="46" t="n"/>
-      <c r="E306" s="46" t="n"/>
-      <c r="F306" s="47" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
